--- a/data/raw/individual/ID 003/continuous/mHLEA_excel/TUM_S003_mHLEA_excel_20250716.xlsx
+++ b/data/raw/individual/ID 003/continuous/mHLEA_excel/TUM_S003_mHLEA_excel_20250716.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sarina/LRZ Sync+Share/Light Logger Study Data/raw/individual/ID 003/continuous/mHLEA_excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zauner/Documents/Arbeit/12-TUM/MeLiDos/WP2.2.5_Data_Analysis/HildenEtAl_Dataset_2025/data/raw/individual/ID 003/continuous/mHLEA_excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139089BC-D7F5-7143-9759-8829F0286B8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E91240-8179-814A-8F00-38BBF0E64B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="680" yWindow="500" windowWidth="19180" windowHeight="10780" xr2:uid="{B80439AF-1263-4DF6-B1CE-F20A60096DC5}"/>
+    <workbookView xWindow="1160" yWindow="780" windowWidth="19180" windowHeight="10780" xr2:uid="{B80439AF-1263-4DF6-B1CE-F20A60096DC5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="20">
   <si>
     <t>timestamp</t>
   </si>
@@ -83,19 +83,19 @@
     <t>O+I</t>
   </si>
   <si>
-    <t>8: Doctor appointment</t>
-  </si>
-  <si>
-    <t>8: online lecture</t>
-  </si>
-  <si>
     <t>I+L</t>
   </si>
   <si>
-    <t>8: doctor appointment</t>
+    <t>Doctor appointment</t>
   </si>
   <si>
-    <t>8: Yoga</t>
+    <t>online lecture</t>
+  </si>
+  <si>
+    <t>doctor appointment</t>
+  </si>
+  <si>
+    <t>Yoga</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>45447.958333333219</v>
@@ -1043,7 +1043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>45447.999999999884</v>
@@ -1055,7 +1055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>45448.041666666548</v>
@@ -1067,7 +1067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <f t="shared" si="0"/>
         <v>45448.083333333212</v>
@@ -1079,7 +1079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <f t="shared" si="0"/>
         <v>45448.124999999876</v>
@@ -1091,7 +1091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <f t="shared" si="0"/>
         <v>45448.166666666541</v>
@@ -1103,7 +1103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <f t="shared" si="0"/>
         <v>45448.208333333205</v>
@@ -1115,7 +1115,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <f t="shared" si="0"/>
         <v>45448.249999999869</v>
@@ -1127,7 +1127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <f t="shared" si="0"/>
         <v>45448.291666666533</v>
@@ -1139,7 +1139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <f t="shared" si="0"/>
         <v>45448.333333333198</v>
@@ -1151,7 +1151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <f t="shared" si="0"/>
         <v>45448.374999999862</v>
@@ -1163,7 +1163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <f t="shared" si="0"/>
         <v>45448.416666666526</v>
@@ -1175,7 +1175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <f t="shared" si="0"/>
         <v>45448.45833333319</v>
@@ -1187,7 +1187,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <f t="shared" si="0"/>
         <v>45448.499999999854</v>
@@ -1195,11 +1195,14 @@
       <c r="B62" t="s">
         <v>10</v>
       </c>
-      <c r="C62" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C62">
+        <v>8</v>
+      </c>
+      <c r="D62" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <f t="shared" si="0"/>
         <v>45448.541666666519</v>
@@ -1211,7 +1214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <f t="shared" si="0"/>
         <v>45448.583333333183</v>
@@ -1415,7 +1418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <f t="shared" si="1"/>
         <v>45449.291666666475</v>
@@ -1427,7 +1430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <f t="shared" si="1"/>
         <v>45449.333333333139</v>
@@ -1439,7 +1442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <f t="shared" si="1"/>
         <v>45449.374999999804</v>
@@ -1451,7 +1454,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <f t="shared" si="1"/>
         <v>45449.416666666468</v>
@@ -1463,7 +1466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <f t="shared" si="1"/>
         <v>45449.458333333132</v>
@@ -1475,7 +1478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <f t="shared" si="1"/>
         <v>45449.499999999796</v>
@@ -1487,7 +1490,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <f t="shared" si="1"/>
         <v>45449.541666666461</v>
@@ -1499,7 +1502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <f t="shared" si="1"/>
         <v>45449.583333333125</v>
@@ -1507,11 +1510,14 @@
       <c r="B88" t="s">
         <v>7</v>
       </c>
-      <c r="C88" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="C88">
+        <v>8</v>
+      </c>
+      <c r="D88" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <f t="shared" si="1"/>
         <v>45449.624999999789</v>
@@ -1522,8 +1528,11 @@
       <c r="C89">
         <v>8</v>
       </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D89" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <f t="shared" si="1"/>
         <v>45449.666666666453</v>
@@ -1535,7 +1544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <f t="shared" si="1"/>
         <v>45449.708333333117</v>
@@ -1547,7 +1556,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <f t="shared" si="1"/>
         <v>45449.749999999782</v>
@@ -1559,7 +1568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <f t="shared" si="1"/>
         <v>45449.791666666446</v>
@@ -1571,7 +1580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <f t="shared" si="1"/>
         <v>45449.83333333311</v>
@@ -1583,7 +1592,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <f t="shared" si="1"/>
         <v>45449.874999999774</v>
@@ -1595,7 +1604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <f t="shared" si="1"/>
         <v>45449.916666666439</v>
@@ -1607,7 +1616,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <f t="shared" si="1"/>
         <v>45449.958333333103</v>
@@ -1619,7 +1628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <f t="shared" si="1"/>
         <v>45449.999999999767</v>
@@ -1631,7 +1640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <f t="shared" si="1"/>
         <v>45450.041666666431</v>
@@ -1643,7 +1652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <f t="shared" si="1"/>
         <v>45450.083333333096</v>
@@ -1655,7 +1664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <f t="shared" si="1"/>
         <v>45450.12499999976</v>
@@ -1667,7 +1676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <f t="shared" si="1"/>
         <v>45450.166666666424</v>
@@ -1679,7 +1688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <f t="shared" si="1"/>
         <v>45450.208333333088</v>
@@ -1691,7 +1700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <f t="shared" si="1"/>
         <v>45450.249999999753</v>
@@ -1703,7 +1712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <f t="shared" si="1"/>
         <v>45450.291666666417</v>
@@ -1715,7 +1724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <f t="shared" si="1"/>
         <v>45450.333333333081</v>
@@ -1727,7 +1736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <f t="shared" si="1"/>
         <v>45450.374999999745</v>
@@ -1739,7 +1748,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <f t="shared" si="1"/>
         <v>45450.41666666641</v>
@@ -1751,19 +1760,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <f t="shared" si="1"/>
         <v>45450.458333333074</v>
       </c>
       <c r="B109" t="s">
-        <v>17</v>
-      </c>
-      <c r="C109" t="s">
+        <v>15</v>
+      </c>
+      <c r="C109">
+        <v>8</v>
+      </c>
+      <c r="D109" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <f t="shared" si="1"/>
         <v>45450.499999999738</v>
@@ -1775,7 +1787,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <f t="shared" si="1"/>
         <v>45450.541666666402</v>
@@ -1787,7 +1799,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <f t="shared" si="1"/>
         <v>45450.583333333067</v>
@@ -1991,7 +2003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <f t="shared" si="1"/>
         <v>45451.291666666359</v>
@@ -2003,7 +2015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <f t="shared" si="1"/>
         <v>45451.333333333023</v>
@@ -2015,7 +2027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <f t="shared" si="1"/>
         <v>45451.374999999687</v>
@@ -2027,7 +2039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <f t="shared" ref="A132:A169" si="2">A131 + TIME(1, 0, 0)</f>
         <v>45451.416666666351</v>
@@ -2039,7 +2051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <f t="shared" si="2"/>
         <v>45451.458333333016</v>
@@ -2051,7 +2063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <f t="shared" si="2"/>
         <v>45451.49999999968</v>
@@ -2063,7 +2075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <f t="shared" si="2"/>
         <v>45451.541666666344</v>
@@ -2075,7 +2087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <f t="shared" si="2"/>
         <v>45451.583333333008</v>
@@ -2087,7 +2099,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <f t="shared" si="2"/>
         <v>45451.624999999673</v>
@@ -2099,7 +2111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <f t="shared" si="2"/>
         <v>45451.666666666337</v>
@@ -2111,7 +2123,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <f t="shared" si="2"/>
         <v>45451.708333333001</v>
@@ -2123,7 +2135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <f t="shared" si="2"/>
         <v>45451.749999999665</v>
@@ -2135,7 +2147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <f t="shared" si="2"/>
         <v>45451.79166666633</v>
@@ -2147,7 +2159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <f t="shared" si="2"/>
         <v>45451.833333332994</v>
@@ -2159,7 +2171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <f t="shared" si="2"/>
         <v>45451.874999999658</v>
@@ -2167,11 +2179,14 @@
       <c r="B143" t="s">
         <v>8</v>
       </c>
-      <c r="C143" t="s">
+      <c r="C143">
+        <v>8</v>
+      </c>
+      <c r="D143" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <f t="shared" si="2"/>
         <v>45451.916666666322</v>
